--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/12_Anotacijos_logai/12_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/12_Anotacijos_logai/12_Anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\12_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC0235E-8BD5-426F-831F-7E2D34047836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAF45AB-1075-42B7-9377-355592B04CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -695,7 +695,7 @@
       <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4" t="b">
+      <c r="F2" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -731,7 +731,7 @@
       <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="4" t="b">
+      <c r="F3" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -765,7 +765,7 @@
       <c r="D4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="4" t="b">
+      <c r="F4" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -797,7 +797,7 @@
       <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4" t="b">
+      <c r="F5" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -831,7 +831,7 @@
       <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4" t="b">
+      <c r="F6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -865,7 +865,7 @@
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="b">
+      <c r="F7" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -899,7 +899,7 @@
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4" t="b">
+      <c r="F8" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -933,7 +933,7 @@
       <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="4" t="b">
+      <c r="F9" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -954,7 +954,7 @@
       <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="4" t="b">
+      <c r="F10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -975,7 +975,7 @@
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="4" t="b">
+      <c r="F11" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="7"/>
